--- a/Data/Salmon/Market/CPI_YOY.xlsx
+++ b/Data/Salmon/Market/CPI_YOY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fillipaskildsen/Documents/GitHub/Data/Salmon/Market/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5ABF77C-E250-8042-9037-4F740B0B10DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6D6347-5AA1-5E49-90E0-E6708B77082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="14" width="13" customWidth="1"/>
@@ -474,515 +474,497 @@
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" s="1">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="C2" s="1">
-        <v>2.2999999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="D2" s="1">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="E2" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="F2" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="1">
-        <v>3.1</v>
-      </c>
-      <c r="H2" s="1">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="J2" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="K2" s="1">
         <v>3.6</v>
       </c>
-      <c r="L2" s="1">
-        <v>3.1</v>
-      </c>
-      <c r="M2" s="1">
-        <v>3</v>
-      </c>
-      <c r="N2" s="1">
-        <v>3.2</v>
-      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1">
         <v>3.2</v>
       </c>
-      <c r="C3" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="D3" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E3" s="1">
-        <v>3.9</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="J3" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K3" s="1">
         <v>3.6</v>
       </c>
-      <c r="G3" s="1">
+      <c r="L3" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="M3" s="1">
         <v>3</v>
       </c>
-      <c r="H3" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="I3" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="J3" s="1">
-        <v>2.7</v>
-      </c>
-      <c r="K3" s="1">
-        <v>3</v>
-      </c>
-      <c r="L3" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="M3" s="1">
-        <v>2.4</v>
-      </c>
       <c r="N3" s="1">
-        <v>2.2999999999999998</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" s="1">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="C4" s="1">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="D4" s="1">
-        <v>6.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E4" s="1">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="F4" s="1">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="G4" s="1">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="H4" s="1">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="I4" s="1">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="1">
-        <v>4.9000000000000004</v>
+        <v>2.7</v>
       </c>
       <c r="K4" s="1">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L4" s="1">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="M4" s="1">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="N4" s="1">
-        <v>4.7</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B5" s="1">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="C5" s="1">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="E5" s="1">
-        <v>4.5999999999999996</v>
+        <v>6.6</v>
       </c>
       <c r="F5" s="1">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="G5" s="1">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H5" s="1">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I5" s="1">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="J5" s="1">
-        <v>6.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="K5" s="1">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="L5" s="1">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M5" s="1">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="N5" s="1">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B6" s="1">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="C6" s="1">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D6" s="1">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="E6" s="1">
-        <v>3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F6" s="1">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="G6" s="1">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="H6" s="1">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="I6" s="1">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J6" s="1">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="K6" s="1">
-        <v>4.0999999999999996</v>
+        <v>6.8</v>
       </c>
       <c r="L6" s="1">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="M6" s="1">
-        <v>5.0999999999999996</v>
+        <v>6.5</v>
       </c>
       <c r="N6" s="1">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B7" s="1">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="C7" s="1">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="1">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="H7" s="1">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="I7" s="1">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="1">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="K7" s="1">
-        <v>1.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L7" s="1">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="M7" s="1">
-        <v>0.7</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="N7" s="1">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B8" s="1">
-        <v>2.2000000000000002</v>
+        <v>1.3</v>
       </c>
       <c r="C8" s="1">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="D8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="F8" s="1">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="1">
-        <v>2.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="I8" s="1">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="N8" s="1">
         <v>1.5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="N8" s="1">
-        <v>1.4</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B9" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
         <v>2.8</v>
       </c>
-      <c r="C9" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2.1</v>
-      </c>
       <c r="F9" s="1">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G9" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="H9" s="1">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="I9" s="1">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J9" s="1">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="K9" s="1">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="L9" s="1">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="M9" s="1">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="N9" s="1">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B10" s="1">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="C10" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="D10" s="1">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E10" s="1">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="F10" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="G10" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="H10" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I10" s="1">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J10" s="1">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="K10" s="1">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="L10" s="1">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="M10" s="1">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="N10" s="1">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B11" s="1">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="C11" s="1">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="D11" s="1">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="E11" s="1">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="F11" s="1">
-        <v>3.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G11" s="1">
-        <v>3.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H11" s="1">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="I11" s="1">
-        <v>4.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="1">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="K11" s="1">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="L11" s="1">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="1">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="N11" s="1">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B12" s="1">
-        <v>2.2000000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="1">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="E12" s="1">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="F12" s="1">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="G12" s="1">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="H12" s="1">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="I12" s="1">
-        <v>1.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J12" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="L12" s="1">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="M12" s="1">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N12" s="1">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B13" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
         <v>2.1</v>
       </c>
-      <c r="C13" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.9</v>
-      </c>
       <c r="H13" s="1">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="I13" s="1">
-        <v>2.2999999999999998</v>
+        <v>1.8</v>
       </c>
       <c r="J13" s="1">
         <v>2</v>
@@ -991,584 +973,628 @@
         <v>2.1</v>
       </c>
       <c r="L13" s="1">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M13" s="1">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="N13" s="1">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B14" s="1">
         <v>2.1</v>
       </c>
       <c r="C14" s="1">
-        <v>1.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.9</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E14" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G14" s="1">
         <v>1.9</v>
       </c>
       <c r="H14" s="1">
-        <v>2.2000000000000002</v>
+        <v>1.9</v>
       </c>
       <c r="I14" s="1">
-        <v>2.9</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J14" s="1">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="L14" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="M14" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N14" s="1">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B15" s="1">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="C15" s="1">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="D15" s="1">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E15" s="1">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F15" s="1">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="G15" s="1">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="H15" s="1">
-        <v>0.3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I15" s="1">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J15" s="1">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="K15" s="1">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M15" s="1">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="N15" s="1">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B16" s="1">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D16" s="1">
         <v>1.2</v>
       </c>
       <c r="E16" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="L16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="1">
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
         <v>1.3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="M16" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B17" s="1">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="C17" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="E17" s="1">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="G17" s="1">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="H17" s="1">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I17" s="1">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" s="1">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="1">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="L17" s="1">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="M17" s="1">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N17" s="1">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B18" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="C18" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="G18" s="1">
         <v>2.5</v>
       </c>
-      <c r="E18" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="G18" s="1">
-        <v>3.2</v>
-      </c>
       <c r="H18" s="1">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="J18" s="1">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K18" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="L18" s="1">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="M18" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N18" s="1">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B19" s="1">
-        <v>3.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C19" s="1">
-        <v>3.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D19" s="1">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="E19" s="1">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="1">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G19" s="1">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H19" s="1">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I19" s="1">
-        <v>4.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J19" s="1">
-        <v>4.4000000000000004</v>
+        <v>1.9</v>
       </c>
       <c r="K19" s="1">
-        <v>5.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L19" s="1">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="M19" s="1">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="N19" s="1">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B20" s="1">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="C20" s="1">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="D20" s="1">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="E20" s="1">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="F20" s="1">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="G20" s="1">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="H20" s="1">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="I20" s="1">
-        <v>0.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J20" s="1">
-        <v>0.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.3</v>
+        <v>5.4</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.2</v>
+        <v>5.5</v>
       </c>
       <c r="M20" s="1">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="N20" s="1">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B21" s="1">
-        <v>2.2999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="C21" s="1">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="D21" s="1">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="E21" s="1">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F21" s="1">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="G21" s="1">
-        <v>2.2999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I21" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J21" s="1">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="K21" s="1">
-        <v>2.7</v>
+        <v>-0.3</v>
       </c>
       <c r="L21" s="1">
-        <v>2.7</v>
+        <v>-0.2</v>
       </c>
       <c r="M21" s="1">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="N21" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B22" s="1">
-        <v>1.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C22" s="1">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="D22" s="1">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="E22" s="1">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="F22" s="1">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="G22" s="1">
-        <v>1.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H22" s="1">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J22" s="1">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K22" s="1">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="L22" s="1">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M22" s="1">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="N22" s="1">
-        <v>1.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B23" s="1">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C23" s="1">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>-1.7</v>
+        <v>0.9</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.7</v>
+        <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H23" s="1">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I23" s="1">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J23" s="1">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="K23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="1">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="M23" s="1">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="N23" s="1">
-        <v>1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B24" s="1">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="C24" s="1">
-        <v>5.0999999999999996</v>
+        <v>-1.8</v>
       </c>
       <c r="D24" s="1">
-        <v>4.9000000000000004</v>
+        <v>-1.7</v>
       </c>
       <c r="E24" s="1">
-        <v>3.9</v>
+        <v>-0.7</v>
       </c>
       <c r="F24" s="1">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="G24" s="1">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I24" s="1">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J24" s="1">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="M24" s="1">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="N24" s="1">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B25" s="1">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="C25" s="1">
-        <v>1.4</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D25" s="1">
-        <v>0.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E25" s="1">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="F25" s="1">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="G25" s="1">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H25" s="1">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="I25" s="1">
         <v>1.6</v>
       </c>
       <c r="J25" s="1">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="K25" s="1">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="L25" s="1">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M25" s="1">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="N25" s="1">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
+        <v>2002</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="M26" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="N26" s="1">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>2001</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B27" s="1">
         <v>3</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C27" s="1">
         <v>3.1</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>3.7</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E27" s="1">
         <v>3.7</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F27" s="1">
         <v>4</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G27" s="1">
         <v>4.2</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H27" s="1">
         <v>3.6</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I27" s="1">
         <v>2.7</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J27" s="1">
         <v>2.6</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K27" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L27" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M27" s="1">
         <v>1.8</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N27" s="1">
         <v>2</v>
       </c>
     </row>
